--- a/Team-Data/2012-13/11-11-2012-13.xlsx
+++ b/Team-Data/2012-13/11-11-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,109 +728,109 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
         <v>48</v>
       </c>
       <c r="I2" t="n">
-        <v>36.6</v>
+        <v>38.3</v>
       </c>
       <c r="J2" t="n">
-        <v>81.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="K2" t="n">
-        <v>0.449</v>
+        <v>0.455</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="M2" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.336</v>
+        <v>0.33</v>
       </c>
       <c r="O2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="R2" t="n">
         <v>10.8</v>
       </c>
-      <c r="P2" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="R2" t="n">
-        <v>10.6</v>
-      </c>
       <c r="S2" t="n">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U2" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="V2" t="n">
-        <v>15.2</v>
+        <v>13.5</v>
       </c>
       <c r="W2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="X2" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.8</v>
+        <v>19.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.8</v>
+        <v>-0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AG2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>11</v>
       </c>
       <c r="AI2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AK2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM2" t="n">
         <v>4</v>
@@ -778,7 +845,7 @@
         <v>29</v>
       </c>
       <c r="AQ2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AR2" t="n">
         <v>21</v>
@@ -787,34 +854,34 @@
         <v>24</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC2" t="n">
         <v>17</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>19</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -921,37 +988,37 @@
         <v>-2.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE3" t="n">
         <v>12</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
         <v>7</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
         <v>6</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM3" t="n">
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
         <v>3</v>
@@ -960,37 +1027,37 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB3" t="n">
         <v>14</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -1025,121 +1092,121 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="n">
         <v>48</v>
       </c>
       <c r="I4" t="n">
-        <v>34.4</v>
+        <v>35.8</v>
       </c>
       <c r="J4" t="n">
-        <v>78.8</v>
+        <v>79</v>
       </c>
       <c r="K4" t="n">
-        <v>0.437</v>
+        <v>0.453</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="M4" t="n">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.358</v>
+        <v>0.378</v>
       </c>
       <c r="O4" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P4" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q4" t="n">
         <v>0.68</v>
       </c>
       <c r="R4" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S4" t="n">
-        <v>31.2</v>
+        <v>28.3</v>
       </c>
       <c r="T4" t="n">
-        <v>42.6</v>
+        <v>39.5</v>
       </c>
       <c r="U4" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="V4" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W4" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>93</v>
+        <v>95.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
         <v>11</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AJ4" t="n">
         <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AL4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="n">
         <v>18</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>27</v>
@@ -1148,22 +1215,22 @@
         <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AU4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY4" t="n">
         <v>17</v>
@@ -1175,10 +1242,10 @@
         <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BC4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
         <v>22</v>
@@ -1300,16 +1367,16 @@
         <v>5</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL5" t="n">
         <v>19</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>20</v>
       </c>
       <c r="AM5" t="n">
         <v>15</v>
@@ -1318,13 +1385,13 @@
         <v>22</v>
       </c>
       <c r="AO5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>10</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11</v>
       </c>
       <c r="AR5" t="n">
         <v>2</v>
@@ -1333,31 +1400,31 @@
         <v>28</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU5" t="n">
         <v>28</v>
       </c>
       <c r="AV5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
         <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
         <v>16</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
         <v>29</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -1467,28 +1534,28 @@
         <v>5.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH6" t="n">
         <v>11</v>
       </c>
       <c r="AI6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ6" t="n">
         <v>21</v>
       </c>
       <c r="AK6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1500,28 +1567,28 @@
         <v>20</v>
       </c>
       <c r="AO6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP6" t="n">
         <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
         <v>14</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
         <v>21</v>
@@ -1530,19 +1597,19 @@
         <v>10</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA6" t="n">
         <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -1571,94 +1638,94 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="H7" t="n">
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>36.3</v>
+        <v>36.7</v>
       </c>
       <c r="J7" t="n">
         <v>82.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.439</v>
+        <v>0.444</v>
       </c>
       <c r="L7" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>23</v>
       </c>
       <c r="N7" t="n">
-        <v>0.385</v>
+        <v>0.399</v>
       </c>
       <c r="O7" t="n">
         <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.655</v>
+        <v>0.649</v>
       </c>
       <c r="R7" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="S7" t="n">
-        <v>28.6</v>
+        <v>29</v>
       </c>
       <c r="T7" t="n">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="V7" t="n">
-        <v>17.9</v>
+        <v>18.3</v>
       </c>
       <c r="W7" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>22.1</v>
+        <v>22.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF7" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AG7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH7" t="n">
         <v>11</v>
@@ -1667,13 +1734,13 @@
         <v>14</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK7" t="n">
         <v>13</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM7" t="n">
         <v>5</v>
@@ -1691,40 +1758,40 @@
         <v>29</v>
       </c>
       <c r="AR7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW7" t="n">
         <v>11</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>8</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
       </c>
       <c r="AY7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ7" t="n">
         <v>24</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -1834,52 +1901,52 @@
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>10</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
         <v>2</v>
       </c>
       <c r="AM8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN8" t="n">
         <v>1</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
         <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,19 +1958,19 @@
         <v>22</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ8" t="n">
         <v>27</v>
       </c>
       <c r="BA8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -2016,31 +2083,31 @@
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ9" t="n">
         <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN9" t="n">
         <v>29</v>
@@ -2049,7 +2116,7 @@
         <v>27</v>
       </c>
       <c r="AP9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
         <v>30</v>
@@ -2070,16 +2137,16 @@
         <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
         <v>6</v>
       </c>
       <c r="AY9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
         <v>17</v>
@@ -2088,7 +2155,7 @@
         <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -2219,16 +2286,16 @@
         <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP10" t="n">
         <v>12</v>
@@ -2246,28 +2313,28 @@
         <v>30</v>
       </c>
       <c r="AU10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW10" t="n">
         <v>28</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
       </c>
       <c r="AZ10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA10" t="n">
         <v>9</v>
       </c>
-      <c r="BA10" t="n">
-        <v>6</v>
-      </c>
       <c r="BB10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC10" t="n">
         <v>30</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -2383,16 +2450,16 @@
         <v>12</v>
       </c>
       <c r="AF11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ11" t="n">
         <v>7</v>
@@ -2401,22 +2468,22 @@
         <v>23</v>
       </c>
       <c r="AL11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>19</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR11" t="n">
         <v>13</v>
@@ -2428,7 +2495,7 @@
         <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
         <v>22</v>
@@ -2437,7 +2504,7 @@
         <v>20</v>
       </c>
       <c r="AX11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY11" t="n">
         <v>19</v>
@@ -2449,7 +2516,7 @@
         <v>2</v>
       </c>
       <c r="BB11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
         <v>21</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -2559,16 +2626,16 @@
         <v>1</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
         <v>7</v>
@@ -2592,13 +2659,13 @@
         <v>27</v>
       </c>
       <c r="AO12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR12" t="n">
         <v>6</v>
@@ -2616,22 +2683,22 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY12" t="n">
         <v>21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
         <v>13</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -2747,16 +2814,16 @@
         <v>12</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>12</v>
@@ -2765,7 +2832,7 @@
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>14</v>
@@ -2774,13 +2841,13 @@
         <v>24</v>
       </c>
       <c r="AO13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR13" t="n">
         <v>4</v>
@@ -2810,13 +2877,13 @@
         <v>2</v>
       </c>
       <c r="BA13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -2845,94 +2912,94 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J14" t="n">
-        <v>77.7</v>
+        <v>77</v>
       </c>
       <c r="K14" t="n">
-        <v>0.496</v>
+        <v>0.502</v>
       </c>
       <c r="L14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.359</v>
+        <v>0.363</v>
       </c>
       <c r="O14" t="n">
-        <v>18.4</v>
+        <v>20.2</v>
       </c>
       <c r="P14" t="n">
-        <v>23.7</v>
+        <v>26.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.777</v>
+        <v>0.766</v>
       </c>
       <c r="R14" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T14" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="W14" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.7</v>
+        <v>22.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>102.1</v>
+        <v>104.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>11</v>
@@ -2941,37 +3008,37 @@
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AN14" t="n">
         <v>10</v>
       </c>
       <c r="AO14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
         <v>25</v>
       </c>
       <c r="AS14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AU14" t="n">
         <v>7</v>
@@ -2983,22 +3050,22 @@
         <v>4</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ14" t="n">
         <v>29</v>
       </c>
       <c r="BA14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -3027,124 +3094,124 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="J15" t="n">
-        <v>77</v>
+        <v>76.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L15" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="M15" t="n">
-        <v>20.7</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="O15" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="P15" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.675</v>
       </c>
       <c r="R15" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="S15" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T15" t="n">
-        <v>47.3</v>
+        <v>46.8</v>
       </c>
       <c r="U15" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="V15" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="W15" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA15" t="n">
         <v>24.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AF15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG15" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AH15" t="n">
         <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK15" t="n">
         <v>7</v>
       </c>
       <c r="AL15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR15" t="n">
         <v>3</v>
@@ -3156,31 +3223,31 @@
         <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
       </c>
       <c r="BB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC15" t="n">
         <v>10</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>9</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -3209,133 +3276,133 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="H16" t="n">
         <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="J16" t="n">
         <v>86.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.431</v>
+        <v>0.429</v>
       </c>
       <c r="L16" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>16.7</v>
+        <v>15.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.39</v>
+        <v>0.329</v>
       </c>
       <c r="O16" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
       <c r="P16" t="n">
-        <v>24.5</v>
+        <v>26.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.802</v>
       </c>
       <c r="R16" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="S16" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="T16" t="n">
-        <v>44.5</v>
+        <v>44.8</v>
       </c>
       <c r="U16" t="n">
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
       <c r="V16" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="W16" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="X16" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="Y16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC16" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z16" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9</v>
-      </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
         <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ16" t="n">
         <v>6</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AM16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP16" t="n">
         <v>5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR16" t="n">
         <v>7</v>
       </c>
       <c r="AS16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU16" t="n">
         <v>9</v>
@@ -3344,25 +3411,25 @@
         <v>7</v>
       </c>
       <c r="AW16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
         <v>25</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BB16" t="n">
         <v>5</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -3391,160 +3458,160 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.714</v>
+        <v>0.833</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>39</v>
+        <v>40.5</v>
       </c>
       <c r="J17" t="n">
         <v>78.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.495</v>
+        <v>0.515</v>
       </c>
       <c r="L17" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="M17" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.412</v>
+        <v>0.429</v>
       </c>
       <c r="O17" t="n">
-        <v>17.7</v>
+        <v>17</v>
       </c>
       <c r="P17" t="n">
-        <v>22.7</v>
+        <v>20.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.78</v>
+        <v>0.829</v>
       </c>
       <c r="R17" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="S17" t="n">
-        <v>31.4</v>
+        <v>32</v>
       </c>
       <c r="T17" t="n">
-        <v>39.6</v>
+        <v>39</v>
       </c>
       <c r="U17" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
       <c r="V17" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W17" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.4</v>
+        <v>107.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.6</v>
+        <v>9.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
         <v>11</v>
       </c>
       <c r="AI17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="n">
         <v>23</v>
       </c>
       <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>2</v>
       </c>
-      <c r="AL17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO17" t="n">
+      <c r="AR17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS17" t="n">
         <v>10</v>
       </c>
-      <c r="AP17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>13</v>
-      </c>
       <c r="AT17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX17" t="n">
         <v>21</v>
       </c>
       <c r="AY17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
         <v>21</v>
       </c>
       <c r="BB17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>0.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>12</v>
       </c>
       <c r="AF18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG18" t="n">
         <v>10</v>
@@ -3666,22 +3733,22 @@
         <v>11</v>
       </c>
       <c r="AI18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ18" t="n">
         <v>10</v>
       </c>
       <c r="AK18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>26</v>
@@ -3702,7 +3769,7 @@
         <v>20</v>
       </c>
       <c r="AU18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV18" t="n">
         <v>19</v>
@@ -3717,10 +3784,10 @@
         <v>4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -3833,34 +3900,34 @@
         <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH19" t="n">
         <v>11</v>
       </c>
       <c r="AI19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ19" t="n">
         <v>24</v>
       </c>
       <c r="AK19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL19" t="n">
         <v>29</v>
       </c>
       <c r="AM19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN19" t="n">
         <v>30</v>
@@ -3869,7 +3936,7 @@
         <v>8</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AQ19" t="n">
         <v>18</v>
@@ -3878,16 +3945,16 @@
         <v>12</v>
       </c>
       <c r="AS19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU19" t="n">
         <v>10</v>
       </c>
       <c r="AV19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW19" t="n">
         <v>19</v>
@@ -3896,7 +3963,7 @@
         <v>7</v>
       </c>
       <c r="AY19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ19" t="n">
         <v>5</v>
@@ -3908,7 +3975,7 @@
         <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>-0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>12</v>
       </c>
       <c r="AF20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG20" t="n">
         <v>10</v>
@@ -4033,16 +4100,16 @@
         <v>29</v>
       </c>
       <c r="AJ20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL20" t="n">
         <v>26</v>
       </c>
-      <c r="AK20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>27</v>
-      </c>
       <c r="AM20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN20" t="n">
         <v>28</v>
@@ -4054,10 +4121,10 @@
         <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
         <v>9</v>
@@ -4072,7 +4139,7 @@
         <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX20" t="n">
         <v>7</v>
@@ -4084,13 +4151,13 @@
         <v>3</v>
       </c>
       <c r="BA20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>17</v>
       </c>
       <c r="AD21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF21" t="n">
         <v>1</v>
@@ -4212,13 +4279,13 @@
         <v>11</v>
       </c>
       <c r="AI21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4230,34 +4297,34 @@
         <v>2</v>
       </c>
       <c r="AO21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
         <v>23</v>
       </c>
       <c r="AS21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY21" t="n">
         <v>2</v>
@@ -4266,10 +4333,10 @@
         <v>4</v>
       </c>
       <c r="BA21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC21" t="n">
         <v>1</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -4301,118 +4368,118 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
         <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>35.7</v>
+        <v>35</v>
       </c>
       <c r="J22" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="L22" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M22" t="n">
-        <v>17.3</v>
+        <v>17.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.413</v>
+        <v>0.406</v>
       </c>
       <c r="O22" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="P22" t="n">
-        <v>25.7</v>
+        <v>26.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.839</v>
+        <v>0.835</v>
       </c>
       <c r="R22" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>34.4</v>
+        <v>34</v>
       </c>
       <c r="T22" t="n">
-        <v>42.1</v>
+        <v>42.3</v>
       </c>
       <c r="U22" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="V22" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="W22" t="n">
         <v>6.7</v>
       </c>
       <c r="X22" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>100.1</v>
+        <v>99.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH22" t="n">
         <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AJ22" t="n">
         <v>30</v>
       </c>
       <c r="AK22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL22" t="n">
         <v>11</v>
       </c>
       <c r="AM22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP22" t="n">
         <v>3</v>
@@ -4421,25 +4488,25 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW22" t="n">
         <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>1</v>
@@ -4448,13 +4515,13 @@
         <v>23</v>
       </c>
       <c r="BA22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB22" t="n">
         <v>7</v>
       </c>
-      <c r="BB22" t="n">
-        <v>6</v>
-      </c>
       <c r="BC22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -4483,52 +4550,52 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="H23" t="n">
         <v>48</v>
       </c>
       <c r="I23" t="n">
-        <v>35.2</v>
+        <v>36.2</v>
       </c>
       <c r="J23" t="n">
-        <v>83</v>
+        <v>82.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.424</v>
+        <v>0.437</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="M23" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.37</v>
+        <v>0.426</v>
       </c>
       <c r="O23" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="P23" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.75</v>
+        <v>0.756</v>
       </c>
       <c r="R23" t="n">
         <v>10.8</v>
       </c>
       <c r="S23" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T23" t="n">
         <v>42.2</v>
@@ -4537,61 +4604,61 @@
         <v>21.8</v>
       </c>
       <c r="V23" t="n">
-        <v>14.3</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="X23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>87.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.7</v>
+        <v>-5.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG23" t="n">
         <v>22</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>24</v>
       </c>
       <c r="AH23" t="n">
         <v>11</v>
       </c>
       <c r="AI23" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>29</v>
       </c>
       <c r="AN23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AO23" t="n">
         <v>28</v>
@@ -4600,7 +4667,7 @@
         <v>28</v>
       </c>
       <c r="AQ23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR23" t="n">
         <v>19</v>
@@ -4612,19 +4679,19 @@
         <v>17</v>
       </c>
       <c r="AU23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
         <v>22</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>0.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH24" t="n">
         <v>11</v>
@@ -4773,7 +4840,7 @@
         <v>17</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
         <v>25</v>
@@ -4782,7 +4849,7 @@
         <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR24" t="n">
         <v>14</v>
@@ -4797,25 +4864,25 @@
         <v>24</v>
       </c>
       <c r="AV24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX24" t="n">
         <v>19</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>28</v>
       </c>
       <c r="BB24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -4931,10 +4998,10 @@
         <v>12</v>
       </c>
       <c r="AF25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH25" t="n">
         <v>11</v>
@@ -4979,7 +5046,7 @@
         <v>25</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
         <v>10</v>
@@ -4988,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="AY25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ25" t="n">
         <v>20</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -5107,13 +5174,13 @@
         <v>-5.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG26" t="n">
         <v>24</v>
@@ -5122,13 +5189,13 @@
         <v>7</v>
       </c>
       <c r="AI26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ26" t="n">
         <v>5</v>
       </c>
       <c r="AK26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
@@ -5137,25 +5204,25 @@
         <v>6</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
         <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ26" t="n">
         <v>20</v>
       </c>
       <c r="AR26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS26" t="n">
         <v>27</v>
       </c>
       <c r="AT26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU26" t="n">
         <v>23</v>
@@ -5164,10 +5231,10 @@
         <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
         <v>8</v>
@@ -5182,7 +5249,7 @@
         <v>9</v>
       </c>
       <c r="BC26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -5211,139 +5278,139 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="I27" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J27" t="n">
-        <v>88.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="K27" t="n">
         <v>0.401</v>
       </c>
       <c r="L27" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>18.4</v>
+        <v>17.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0.295</v>
+        <v>0.292</v>
       </c>
       <c r="O27" t="n">
-        <v>15.1</v>
+        <v>15.8</v>
       </c>
       <c r="P27" t="n">
-        <v>19.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
       <c r="R27" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="S27" t="n">
-        <v>29.4</v>
+        <v>30.2</v>
       </c>
       <c r="T27" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="U27" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="V27" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W27" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>17.7</v>
+        <v>18.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>91.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.6</v>
+        <v>-5.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF27" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AG27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
         <v>1</v>
       </c>
       <c r="AI27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
         <v>30</v>
       </c>
       <c r="AL27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AM27" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AN27" t="n">
         <v>26</v>
       </c>
       <c r="AO27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
         <v>8</v>
       </c>
       <c r="AS27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AT27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW27" t="n">
         <v>5</v>
@@ -5358,13 +5425,13 @@
         <v>30</v>
       </c>
       <c r="BA27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB27" t="n">
         <v>24</v>
       </c>
       <c r="BC27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -5486,40 +5553,40 @@
         <v>11</v>
       </c>
       <c r="AI28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK28" t="n">
         <v>3</v>
       </c>
       <c r="AL28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO28" t="n">
         <v>12</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>13</v>
       </c>
       <c r="AP28" t="n">
         <v>15</v>
       </c>
       <c r="AQ28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS28" t="n">
         <v>14</v>
       </c>
-      <c r="AR28" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>13</v>
-      </c>
       <c r="AT28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5528,16 +5595,16 @@
         <v>24</v>
       </c>
       <c r="AW28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY28" t="n">
         <v>18</v>
       </c>
       <c r="AZ28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA28" t="n">
         <v>19</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>-4.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>28</v>
       </c>
       <c r="AF29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG29" t="n">
         <v>28</v>
@@ -5677,22 +5744,22 @@
         <v>28</v>
       </c>
       <c r="AL29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM29" t="n">
         <v>6</v>
       </c>
       <c r="AN29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
         <v>9</v>
       </c>
       <c r="AP29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR29" t="n">
         <v>18</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
@@ -5713,7 +5780,7 @@
         <v>11</v>
       </c>
       <c r="AX29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY29" t="n">
         <v>23</v>
@@ -5722,10 +5789,10 @@
         <v>28</v>
       </c>
       <c r="BA29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -5841,28 +5908,28 @@
         <v>12</v>
       </c>
       <c r="AF30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH30" t="n">
         <v>11</v>
       </c>
       <c r="AI30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ30" t="n">
         <v>11</v>
       </c>
       <c r="AK30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN30" t="n">
         <v>25</v>
@@ -5871,7 +5938,7 @@
         <v>20</v>
       </c>
       <c r="AP30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ30" t="n">
         <v>22</v>
@@ -5883,16 +5950,16 @@
         <v>10</v>
       </c>
       <c r="AT30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV30" t="n">
         <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX30" t="n">
         <v>1</v>
@@ -5907,7 +5974,7 @@
         <v>19</v>
       </c>
       <c r="BB30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-6.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6032,7 +6099,7 @@
         <v>5</v>
       </c>
       <c r="AI31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
@@ -6041,7 +6108,7 @@
         <v>25</v>
       </c>
       <c r="AL31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM31" t="n">
         <v>3</v>
@@ -6050,7 +6117,7 @@
         <v>21</v>
       </c>
       <c r="AO31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP31" t="n">
         <v>30</v>
@@ -6062,19 +6129,19 @@
         <v>24</v>
       </c>
       <c r="AS31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT31" t="n">
         <v>21</v>
       </c>
       <c r="AU31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV31" t="n">
         <v>21</v>
       </c>
       <c r="AW31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX31" t="n">
         <v>14</v>
@@ -6089,7 +6156,7 @@
         <v>29</v>
       </c>
       <c r="BB31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-11-2012-13</t>
+          <t>2012-11-11</t>
         </is>
       </c>
     </row>
